--- a/Timesheet Eclipse.xlsx
+++ b/Timesheet Eclipse.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a31e8c8f31ec5ad0/Documents/Duane TimeSheets/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/A31E8C8F31EC5AD0/Documents/Duane TimeSheets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="27" documentId="13_ncr:1_{3EE6EAE6-F307-4E94-9AB9-44A2A5173D99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5F83B4E9-FE9B-4EE9-82F4-8257075D6C85}"/>
+  <xr:revisionPtr revIDLastSave="1396" documentId="13_ncr:1_{3EE6EAE6-F307-4E94-9AB9-44A2A5173D99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5C05220A-AB95-407E-A9EF-EE6826E3A794}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="651" uniqueCount="309">
   <si>
     <t>Compnay</t>
   </si>
@@ -180,6 +180,789 @@
   </si>
   <si>
     <t>Showed Khadija how to add a location</t>
+  </si>
+  <si>
+    <t>Assisted Viwe with his purchase orders approvals</t>
+  </si>
+  <si>
+    <t>Reset Hectors password</t>
+  </si>
+  <si>
+    <t>Assisted Christina with a purchase orders status</t>
+  </si>
+  <si>
+    <t>Assisted Veronica with her approvals</t>
+  </si>
+  <si>
+    <t>Advised Anisha on a rate item.</t>
+  </si>
+  <si>
+    <t>SHO</t>
+  </si>
+  <si>
+    <t>Added items for Veronica</t>
+  </si>
+  <si>
+    <t>Advised Isa on her approvals</t>
+  </si>
+  <si>
+    <t>Added Herman to Eclipse</t>
+  </si>
+  <si>
+    <t>Advised Refiloe on an account</t>
+  </si>
+  <si>
+    <t>Adjusted Kelebogile's approvals</t>
+  </si>
+  <si>
+    <t>Assisted Sharon with a GRN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Updated Arshad's approvals </t>
+  </si>
+  <si>
+    <t>Assisted Nicole with a enquiry on rates</t>
+  </si>
+  <si>
+    <t>Re-instated a purchase order for Geoffrey</t>
+  </si>
+  <si>
+    <t>Updated Phindile's menu</t>
+  </si>
+  <si>
+    <t>Assisted Sarusha with a rate on an old shipment</t>
+  </si>
+  <si>
+    <t>Assisted Hector with Items allocation</t>
+  </si>
+  <si>
+    <t>Assisted Sandra with her logging into Eclipse</t>
+  </si>
+  <si>
+    <t>Assisted Gregory with his approvals</t>
+  </si>
+  <si>
+    <t>Assisted Anna with a shipment</t>
+  </si>
+  <si>
+    <t>Assisted Esethu with Andrew's approvals</t>
+  </si>
+  <si>
+    <t>Switched on Isa's approvals on level 1</t>
+  </si>
+  <si>
+    <t>Adjusted Andrew's menu access</t>
+  </si>
+  <si>
+    <t>Checked Sello's template</t>
+  </si>
+  <si>
+    <t>Adjusted Nozuko's approvals on Cashbook</t>
+  </si>
+  <si>
+    <t>Advised Joneil on her shipment</t>
+  </si>
+  <si>
+    <t>Adjust Marijela's approvals</t>
+  </si>
+  <si>
+    <t>Updated the rates for Leonie</t>
+  </si>
+  <si>
+    <t>Updated the recon process flow for Karien</t>
+  </si>
+  <si>
+    <t>Updated the supplier master auth for GFCB</t>
+  </si>
+  <si>
+    <t>Updated the line rates on Shell for JHB for Aalia</t>
+  </si>
+  <si>
+    <t>Advised leonie on why certain shipments are verified</t>
+  </si>
+  <si>
+    <t>Added cost centres on for Maralin</t>
+  </si>
+  <si>
+    <t>Updated the rates for Durban Lubricants</t>
+  </si>
+  <si>
+    <t>Worked on the Eclipse Web app</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T006244 </t>
+  </si>
+  <si>
+    <t>Opened an account for Thabang</t>
+  </si>
+  <si>
+    <t>Advised Leonie on a customer</t>
+  </si>
+  <si>
+    <t>Assisted Laurika with her cost centres</t>
+  </si>
+  <si>
+    <t>Changed Laurika's authorization on WP</t>
+  </si>
+  <si>
+    <t>Provided a report on PO,proforma etc to Karien.</t>
+  </si>
+  <si>
+    <t>Created Dirk Uijs' vehicle</t>
+  </si>
+  <si>
+    <t>Advised Georgina on a PO Approval</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adjusted Ntsekiseng's access </t>
+  </si>
+  <si>
+    <t>Advised Sharon on a purchase order</t>
+  </si>
+  <si>
+    <t>Advised Yvette on a cost centre</t>
+  </si>
+  <si>
+    <t>Reset Riaan</t>
+  </si>
+  <si>
+    <t>Assisted Sarusha with deleteing an item off a batch</t>
+  </si>
+  <si>
+    <t>Assisted Marijela with a supplier credit</t>
+  </si>
+  <si>
+    <t>Assisted Tshiamo with a purchase order</t>
+  </si>
+  <si>
+    <t>Reinstated a purchase order for Sello</t>
+  </si>
+  <si>
+    <t>Advised Darshni on a supplier credit note</t>
+  </si>
+  <si>
+    <t>Assisted Jabulani with Trips and shipments</t>
+  </si>
+  <si>
+    <t>Assisted Shatho with Vehicle master</t>
+  </si>
+  <si>
+    <t>Adjusted the rate locations for Journal Ex Durban</t>
+  </si>
+  <si>
+    <t>Adjusted the name of the rates for Amka</t>
+  </si>
+  <si>
+    <t>Opened an account for Theresa</t>
+  </si>
+  <si>
+    <t>Updated the rates for Shell</t>
+  </si>
+  <si>
+    <t>Taz</t>
+  </si>
+  <si>
+    <t>Changed the ivoicing details for Taz</t>
+  </si>
+  <si>
+    <t>Changed Johan's level amount on his authorizations</t>
+  </si>
+  <si>
+    <t>Updated the rates for Puma</t>
+  </si>
+  <si>
+    <t>GRD</t>
+  </si>
+  <si>
+    <t>Assisted Stanley with an item</t>
+  </si>
+  <si>
+    <t>Reset Khethiwe's Password</t>
+  </si>
+  <si>
+    <t>Updated the rates for Plastomark</t>
+  </si>
+  <si>
+    <t>Showed Zandi how to display ships and trips</t>
+  </si>
+  <si>
+    <t>Assisted Laurika with displaying a supplier on her approvals</t>
+  </si>
+  <si>
+    <t>Advised Jeffrey what went wrong on a purchase order</t>
+  </si>
+  <si>
+    <t>Updated the rates for Sasol</t>
+  </si>
+  <si>
+    <t>Updated the rates for Buckman</t>
+  </si>
+  <si>
+    <t>Updated the rates for Tetrapack</t>
+  </si>
+  <si>
+    <t>Updated the rates for Tanker Services</t>
+  </si>
+  <si>
+    <t>Added a location for Tashne</t>
+  </si>
+  <si>
+    <t>Updated Rates for Motus</t>
+  </si>
+  <si>
+    <t>Advised Tshiamo on a purchase order.</t>
+  </si>
+  <si>
+    <t>TRANSPORT HOLDING</t>
+  </si>
+  <si>
+    <t>Installed Eclipse on Wanika's machine</t>
+  </si>
+  <si>
+    <t>Added a line rate for Sasol</t>
+  </si>
+  <si>
+    <t>Added Anooj to Eclipse</t>
+  </si>
+  <si>
+    <t>Updated the remaining rates for Leonie rates</t>
+  </si>
+  <si>
+    <t>Advised Maudi on what happened to a credit batch approval</t>
+  </si>
+  <si>
+    <t>Assisted Palesa with installing Eclipse on her machine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Changed the rates of Journal Ex Durban </t>
+  </si>
+  <si>
+    <t>Added Supplier payment to Malien and Hoosain</t>
+  </si>
+  <si>
+    <t>Advised Maitumelo on the sdates on her shipments</t>
+  </si>
+  <si>
+    <t>Advised Hayley on andrew approving a RFA</t>
+  </si>
+  <si>
+    <t>Added Vehicle Transactions history to Shatho and Anooj</t>
+  </si>
+  <si>
+    <t>Sho</t>
+  </si>
+  <si>
+    <t>Added an item for Veronica</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Updated the Radius Per Item </t>
+  </si>
+  <si>
+    <t>Opened accounts for PNP</t>
+  </si>
+  <si>
+    <t>Assisted Illana with the status of a PO</t>
+  </si>
+  <si>
+    <t>Deleted a supplier for Laurika</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ASP </t>
+  </si>
+  <si>
+    <t>Advised Sajna on a WIP number</t>
+  </si>
+  <si>
+    <t>Mirrored the Clover SCS and PNP SCS cost centres.</t>
+  </si>
+  <si>
+    <t>Assisted Deisile with the new cost centres on Clover , approvals</t>
+  </si>
+  <si>
+    <t>Sent through process flow reports to Karien</t>
+  </si>
+  <si>
+    <t>Assisted Karien Paoli with changing some users menu on RFDC</t>
+  </si>
+  <si>
+    <t>Added Cost centres to Lizelle</t>
+  </si>
+  <si>
+    <t>DEV</t>
+  </si>
+  <si>
+    <t>Worked on the App</t>
+  </si>
+  <si>
+    <t>Added Haiden cost centres to Elaines profile</t>
+  </si>
+  <si>
+    <t>Advised Theresa on why a certain supplier does not work on purchase orders</t>
+  </si>
+  <si>
+    <t>Advised Zelna on which users can create suppliers for Specific companies</t>
+  </si>
+  <si>
+    <t>Advise Sarusha what is happening with the rates on certain shipments</t>
+  </si>
+  <si>
+    <t>removed Nicole email address from all th mails on 001</t>
+  </si>
+  <si>
+    <t>Advised Chrystal on Vehicle transaction</t>
+  </si>
+  <si>
+    <t>Added the new details on Clover SCS</t>
+  </si>
+  <si>
+    <t>Advised Hayley on what approvals Tobie has</t>
+  </si>
+  <si>
+    <t>Created a new menu grouping on RFDC and made adjustments on the menus on RFDC for Ripfumelo</t>
+  </si>
+  <si>
+    <t>Opened accounts for Maralin</t>
+  </si>
+  <si>
+    <t>Gave Elzet access to cost centres</t>
+  </si>
+  <si>
+    <t>Gave Tobie approval access on 2 cost centres</t>
+  </si>
+  <si>
+    <t>Added cost centres on Hayley's profile</t>
+  </si>
+  <si>
+    <t>Opened accounts for Theresa</t>
+  </si>
+  <si>
+    <t>Advised Maudi with GRN'ng a Purchase order</t>
+  </si>
+  <si>
+    <t>Adjusted Andrew's access on RFDC</t>
+  </si>
+  <si>
+    <t>Removed cost centres from a report for Sello</t>
+  </si>
+  <si>
+    <t>Reset Isa's password</t>
+  </si>
+  <si>
+    <t>Deactivated Thandeka's profile</t>
+  </si>
+  <si>
+    <t>Assisted Sharon with Purchase order approval</t>
+  </si>
+  <si>
+    <t>Advised Andrew on users using Vehicle profitability</t>
+  </si>
+  <si>
+    <t>Worked on adding suppliers to the new company</t>
+  </si>
+  <si>
+    <t>PA Stemmet</t>
+  </si>
+  <si>
+    <t>Deactivated duplicate users for Ripfumelo</t>
+  </si>
+  <si>
+    <t>Removed ID's on certain users for Ripfumelo</t>
+  </si>
+  <si>
+    <t>Advised Shirley on the amounts wrong on her PO</t>
+  </si>
+  <si>
+    <t>Assisted Leonie with a an entry date on a trip/shipment</t>
+  </si>
+  <si>
+    <t>reset Nonhlanhla's password</t>
+  </si>
+  <si>
+    <t>Reset Catherines Password</t>
+  </si>
+  <si>
+    <t>Assisted Theresa with opening an account</t>
+  </si>
+  <si>
+    <t>Changed the menu access of Shared Serv Creditors With Inv posting</t>
+  </si>
+  <si>
+    <t>Gave Tanya's the same cost centres as Sharleen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Added a cost centre on for RE4000 </t>
+  </si>
+  <si>
+    <t>Adjusted Karin's approval access on purchase orders</t>
+  </si>
+  <si>
+    <t>Assisted Shoni with a RFA for Esethu</t>
+  </si>
+  <si>
+    <t>Worked on adding suppliers to the new company PA Stemmet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deactivated users for Deen </t>
+  </si>
+  <si>
+    <t>Added 01100247 on EX6850</t>
+  </si>
+  <si>
+    <t>Deactivated Illana on Eclipse</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reinstated Purchase Orders for Tina </t>
+  </si>
+  <si>
+    <t>Assisted Delisile with GRN'ng a PO</t>
+  </si>
+  <si>
+    <t>Assisted Sarusha with kilometres on her shipment</t>
+  </si>
+  <si>
+    <t>Opened an account for Nwabisa</t>
+  </si>
+  <si>
+    <t>Assisted Rudolph with a credit note approval</t>
+  </si>
+  <si>
+    <t>Assisted Karien with an audit enquiry</t>
+  </si>
+  <si>
+    <t>Reset Nardine's password</t>
+  </si>
+  <si>
+    <t>Assisted Khadija with an exception</t>
+  </si>
+  <si>
+    <t>Assisted Regopotswe with creating Fuel pump</t>
+  </si>
+  <si>
+    <t>Reinstalled Eclipse on Carikes's Machine</t>
+  </si>
+  <si>
+    <t>Reset Mohsin password</t>
+  </si>
+  <si>
+    <t>Reset Naiem's password</t>
+  </si>
+  <si>
+    <t>De-activaated users for Cherrylean</t>
+  </si>
+  <si>
+    <t>Assisted Wanele with exporting her files</t>
+  </si>
+  <si>
+    <t>Helped Tina Reinstate a Purchase order</t>
+  </si>
+  <si>
+    <t>Installed the test Environment for Mduduzi</t>
+  </si>
+  <si>
+    <t>Assisted Sello with updating vehicles on Eclipse</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Advised Saffiyya on the status of a purchase order </t>
+  </si>
+  <si>
+    <t>Granted Patricia access to a cost centre</t>
+  </si>
+  <si>
+    <t>Assisted Refiloe with a purchase order</t>
+  </si>
+  <si>
+    <t>Assisted Sphamandla with a purchase order approval.</t>
+  </si>
+  <si>
+    <t>Assisted Sello with updating details on Vehicle master</t>
+  </si>
+  <si>
+    <t>Opened an account for Laurika</t>
+  </si>
+  <si>
+    <t>Reset Nomagugu's password</t>
+  </si>
+  <si>
+    <t>Assisted Jaqueline with opening a trip</t>
+  </si>
+  <si>
+    <t>Assisted Farrel with  printing a job card</t>
+  </si>
+  <si>
+    <t>Assisted Wanika with logging into Eclipse</t>
+  </si>
+  <si>
+    <t>Argonaut</t>
+  </si>
+  <si>
+    <t>Assisted Ashley with resetting his password.</t>
+  </si>
+  <si>
+    <t>AlF</t>
+  </si>
+  <si>
+    <t>Added companies to Justine's profile</t>
+  </si>
+  <si>
+    <t>Created users for Wanika</t>
+  </si>
+  <si>
+    <t>Reset Sarusha's password</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Updated Lizelle's approvals on credits and PO's </t>
+  </si>
+  <si>
+    <t>Removed the Sello from credit note approvals</t>
+  </si>
+  <si>
+    <t>Reset Kabellos password</t>
+  </si>
+  <si>
+    <t>Advised Karien on a GRN</t>
+  </si>
+  <si>
+    <t>Advised Nwabisa on approvals on the system</t>
+  </si>
+  <si>
+    <t>Updated a rate for Tetrapack</t>
+  </si>
+  <si>
+    <t>Opened an account for Christelle</t>
+  </si>
+  <si>
+    <t>Opened accounts for Thabang</t>
+  </si>
+  <si>
+    <t>Opened an account for Delisile</t>
+  </si>
+  <si>
+    <t>Advised Christelle on why a PO is not going through</t>
+  </si>
+  <si>
+    <t>Changed the company name on an invoice</t>
+  </si>
+  <si>
+    <t>SHo</t>
+  </si>
+  <si>
+    <t>Sent Carike a location list on Shozaloza</t>
+  </si>
+  <si>
+    <t>Reset Anban's password</t>
+  </si>
+  <si>
+    <t>Advised Chrystal on who can delete a job card.</t>
+  </si>
+  <si>
+    <t>Advised Mthunzi on why he couldn’t post an invoice</t>
+  </si>
+  <si>
+    <t>Assisted Kandy with seeing what PO's are needed for approval</t>
+  </si>
+  <si>
+    <t>Updated the rates for Puma Energy</t>
+  </si>
+  <si>
+    <t>Assisted Aalia with a rate for Lubrizol</t>
+  </si>
+  <si>
+    <t>Assisted Stanley with logging into Eclipse</t>
+  </si>
+  <si>
+    <t>Created an account for Delisle</t>
+  </si>
+  <si>
+    <t>EXO</t>
+  </si>
+  <si>
+    <t>Assisted Sarusha with customer trans export template</t>
+  </si>
+  <si>
+    <t>Deactivated Veronica on Eclipse</t>
+  </si>
+  <si>
+    <t>Assisted Clive with logging onto Eclipse</t>
+  </si>
+  <si>
+    <t>Updated the rates for Columbus</t>
+  </si>
+  <si>
+    <t>Opened an account for Dimakatso</t>
+  </si>
+  <si>
+    <t>Advised Sajna with how to check for her DRN's</t>
+  </si>
+  <si>
+    <t>Added a rate line for Leonie</t>
+  </si>
+  <si>
+    <t>Reset Thabiso's password</t>
+  </si>
+  <si>
+    <t>Assisted Tashne with the rates on Tetrapack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assisted Leonie with a rate on Puma </t>
+  </si>
+  <si>
+    <t>Added Ravi and Luthando to Eclipse.</t>
+  </si>
+  <si>
+    <t>Assisted Hector with showing the value of all the items in his store</t>
+  </si>
+  <si>
+    <t>Reset Theresa's password.</t>
+  </si>
+  <si>
+    <t>Reset alton's password</t>
+  </si>
+  <si>
+    <t>Reinstated a Purchase order for Tina</t>
+  </si>
+  <si>
+    <t>Advised Eva on what to do with a credit note</t>
+  </si>
+  <si>
+    <t>Opened an account for Nicole</t>
+  </si>
+  <si>
+    <t>Assisted Mohsin with checking an email</t>
+  </si>
+  <si>
+    <t>Reinstated a purchase order for Matimu</t>
+  </si>
+  <si>
+    <t>Advised Sarusha on how to add a trailer</t>
+  </si>
+  <si>
+    <t>Opened accounts for Zelna</t>
+  </si>
+  <si>
+    <t>Reset Kevins password</t>
+  </si>
+  <si>
+    <t>Assisted Karien with a list of Purchase orders created in 2024</t>
+  </si>
+  <si>
+    <t>Added a menu item on for Karien</t>
+  </si>
+  <si>
+    <t>Support</t>
+  </si>
+  <si>
+    <t>Worked on Restoring BU3 CFLD</t>
+  </si>
+  <si>
+    <t>Opened an account for Wanele</t>
+  </si>
+  <si>
+    <t>Reset Ntsebe's password</t>
+  </si>
+  <si>
+    <t>Advised Sajna on a credit</t>
+  </si>
+  <si>
+    <t>Assisted Carike with the terms and conditions on a with quoatation</t>
+  </si>
+  <si>
+    <t>Reset Isaac's password</t>
+  </si>
+  <si>
+    <t>Adjusted approvals for Geoffrey</t>
+  </si>
+  <si>
+    <t>Assisted Philantha with a change of a supplier ID</t>
+  </si>
+  <si>
+    <t>Opened an accoutn for Nwabisa</t>
+  </si>
+  <si>
+    <t>Adjusted Naiem's access on Eclipse</t>
+  </si>
+  <si>
+    <t>Gave Jane,Andrew, Mduduzi  and Hayley access to CL companies</t>
+  </si>
+  <si>
+    <t>Added Bibiana to Eclipse</t>
+  </si>
+  <si>
+    <t>Assisted Rahaba with loggining into Eclipse</t>
+  </si>
+  <si>
+    <t>Advised Philantha on how to reverse a job card</t>
+  </si>
+  <si>
+    <t>Advised Dineo on how to offset credits on her side.</t>
+  </si>
+  <si>
+    <t>Assisted Marileze with installing Eclipse</t>
+  </si>
+  <si>
+    <t>Added a menu item on for Darshni</t>
+  </si>
+  <si>
+    <t>Advised Jane on what happened to a PO</t>
+  </si>
+  <si>
+    <t>Reset Toni's password</t>
+  </si>
+  <si>
+    <t>Advised Nardine when a PO was authorised</t>
+  </si>
+  <si>
+    <t>Assisted Denise with a shell import</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Added a menu item on Phatu and Philantha's </t>
+  </si>
+  <si>
+    <t>Assisted Melissa with items not yet GRN'd</t>
+  </si>
+  <si>
+    <t>Adjusted Tobies approvals and deactivated Dheven on Eclipse</t>
+  </si>
+  <si>
+    <t>Increased the load capacity for a trip</t>
+  </si>
+  <si>
+    <t>Advised Chrystal on what to do with a markup on a job card</t>
+  </si>
+  <si>
+    <t>Added Casseus to Eclipse</t>
+  </si>
+  <si>
+    <t>Switched on Frikkies notifiactions on level 1</t>
+  </si>
+  <si>
+    <t>Tested the mobile app's trips</t>
+  </si>
+  <si>
+    <t>Reset Casseus' password</t>
+  </si>
+  <si>
+    <t>Assisted with saving Collen on for SAF and ALF</t>
+  </si>
+  <si>
+    <t>Added Kishan to Eclipse</t>
+  </si>
+  <si>
+    <t>Advised Maryann on how to use the correct rate for Astron</t>
+  </si>
+  <si>
+    <t>Assisted with Tobie's approvals</t>
+  </si>
+  <si>
+    <t>Changed Emer and Anban's approval levels on Eclipse</t>
+  </si>
+  <si>
+    <t>Advised Tashne on how to use the correct rate for Astron</t>
+  </si>
+  <si>
+    <t>Opened an account for Maralin Pieterson</t>
+  </si>
+  <si>
+    <t>Added Cohen to Eclipse</t>
   </si>
 </sst>
 </file>
@@ -247,12 +1030,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -268,10 +1052,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -537,12 +1317,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:D47"/>
+  <dimension ref="A2:I376"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.28515625" customWidth="1"/>
     <col min="2" max="3" width="11.140625" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="69.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="91.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -1135,6 +1915,4204 @@
         <v>47</v>
       </c>
     </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A48" s="2">
+        <v>45705</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>19</v>
+      </c>
+      <c r="B49" s="3">
+        <v>0.34375</v>
+      </c>
+      <c r="C49" s="3">
+        <v>0.34375</v>
+      </c>
+      <c r="D49" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>34</v>
+      </c>
+      <c r="B50" s="3">
+        <v>0.34375</v>
+      </c>
+      <c r="C50" s="3">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D50" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>19</v>
+      </c>
+      <c r="B51" s="3">
+        <v>0.36458333333333331</v>
+      </c>
+      <c r="C51" s="3">
+        <v>0.375</v>
+      </c>
+      <c r="D51" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>19</v>
+      </c>
+      <c r="B52" s="3">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="C52" s="3">
+        <v>0.36458333333333331</v>
+      </c>
+      <c r="D52" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>19</v>
+      </c>
+      <c r="B53" s="3">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="C53" s="3">
+        <v>0.4375</v>
+      </c>
+      <c r="D53" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>53</v>
+      </c>
+      <c r="B54" s="3">
+        <v>0.4375</v>
+      </c>
+      <c r="C54" s="3">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D54" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A55" s="2">
+        <v>45707</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>19</v>
+      </c>
+      <c r="B56" s="3">
+        <v>0.4375</v>
+      </c>
+      <c r="C56" s="3">
+        <v>0.44791666666666669</v>
+      </c>
+      <c r="D56" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>19</v>
+      </c>
+      <c r="B57" s="3">
+        <v>0.51041666666666663</v>
+      </c>
+      <c r="C57" s="3">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="D57" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>19</v>
+      </c>
+      <c r="B58" s="3">
+        <v>0.5625</v>
+      </c>
+      <c r="C58" s="3">
+        <v>0.57291666666666663</v>
+      </c>
+      <c r="D58" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>19</v>
+      </c>
+      <c r="B59" s="3">
+        <v>0.67708333333333337</v>
+      </c>
+      <c r="C59" s="3">
+        <v>0.6875</v>
+      </c>
+      <c r="D59" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A60" s="2">
+        <v>45708</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>19</v>
+      </c>
+      <c r="B61" s="3">
+        <v>0.34375</v>
+      </c>
+      <c r="C61" s="3">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D61" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>19</v>
+      </c>
+      <c r="B62" s="3">
+        <v>0.42708333333333331</v>
+      </c>
+      <c r="C62" s="3">
+        <v>0.4375</v>
+      </c>
+      <c r="D62" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>19</v>
+      </c>
+      <c r="B63" s="3">
+        <v>0.48958333333333331</v>
+      </c>
+      <c r="C63" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="D63" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>19</v>
+      </c>
+      <c r="B64" s="3">
+        <v>0.57291666666666663</v>
+      </c>
+      <c r="C64" s="3">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D64" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A65" s="2">
+        <v>45709</v>
+      </c>
+      <c r="H65" t="s">
+        <v>84</v>
+      </c>
+      <c r="I65" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>24</v>
+      </c>
+      <c r="B66" s="3">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="C66" s="3">
+        <v>0.53125</v>
+      </c>
+      <c r="D66" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A67" s="2">
+        <v>45712</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>19</v>
+      </c>
+      <c r="B68" s="3">
+        <v>0.44791666666666669</v>
+      </c>
+      <c r="C68" s="3">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D68" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A69" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="B69" s="3">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="C69" s="3">
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="D69" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>24</v>
+      </c>
+      <c r="B70" s="3">
+        <v>0.51041666666666663</v>
+      </c>
+      <c r="C70" s="3">
+        <v>0.53125</v>
+      </c>
+      <c r="D70" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A71" s="2">
+        <v>45713</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>19</v>
+      </c>
+      <c r="B72" s="3">
+        <v>0.36458333333333331</v>
+      </c>
+      <c r="C72" s="3">
+        <v>0.375</v>
+      </c>
+      <c r="D72" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>19</v>
+      </c>
+      <c r="B73" s="3">
+        <v>0.44791666666666669</v>
+      </c>
+      <c r="C73" s="3">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D73" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>24</v>
+      </c>
+      <c r="B74" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="C74" s="3">
+        <v>0.625</v>
+      </c>
+      <c r="D74" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>19</v>
+      </c>
+      <c r="B75" s="3">
+        <v>0.67708333333333337</v>
+      </c>
+      <c r="C75" s="3">
+        <v>0.6875</v>
+      </c>
+      <c r="D75" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A76" s="2">
+        <v>45714</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>19</v>
+      </c>
+      <c r="B77" s="3">
+        <v>0.59375</v>
+      </c>
+      <c r="C77" s="3">
+        <v>0.61458333333333337</v>
+      </c>
+      <c r="D77" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>19</v>
+      </c>
+      <c r="B78" s="3">
+        <v>0.61458333333333337</v>
+      </c>
+      <c r="C78" s="3">
+        <v>0.625</v>
+      </c>
+      <c r="D78" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>19</v>
+      </c>
+      <c r="B79" s="3">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="C79" s="3">
+        <v>0.65625</v>
+      </c>
+      <c r="D79" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A80" s="2">
+        <v>45715</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>19</v>
+      </c>
+      <c r="B81" s="3">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="C81" s="3">
+        <v>0.34375</v>
+      </c>
+      <c r="D81" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>19</v>
+      </c>
+      <c r="B82" s="3">
+        <v>0.375</v>
+      </c>
+      <c r="C82" s="3">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="D82" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>19</v>
+      </c>
+      <c r="B83" s="3">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="C83" s="3">
+        <v>0.40625</v>
+      </c>
+      <c r="D83" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>19</v>
+      </c>
+      <c r="B84" s="3">
+        <v>0.4375</v>
+      </c>
+      <c r="C84" s="3">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D84" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>19</v>
+      </c>
+      <c r="B85" s="3">
+        <v>0.59375</v>
+      </c>
+      <c r="C85" s="3">
+        <v>0.61458333333333337</v>
+      </c>
+      <c r="D85" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>19</v>
+      </c>
+      <c r="B86" s="3">
+        <v>0.63541666666666663</v>
+      </c>
+      <c r="C86" s="3">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="D86" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A87" s="2">
+        <v>45716</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>19</v>
+      </c>
+      <c r="B88" s="3">
+        <v>0.375</v>
+      </c>
+      <c r="C88" s="3">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="D88" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>19</v>
+      </c>
+      <c r="B89" s="3">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="C89" s="3">
+        <v>0.40625</v>
+      </c>
+      <c r="D89" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>19</v>
+      </c>
+      <c r="B90" s="3">
+        <v>0.4375</v>
+      </c>
+      <c r="C90" s="3">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D90" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>19</v>
+      </c>
+      <c r="B91" s="3">
+        <v>0.46875</v>
+      </c>
+      <c r="C91" s="3">
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="D91" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>19</v>
+      </c>
+      <c r="B92" s="3">
+        <v>0.51041666666666663</v>
+      </c>
+      <c r="C92" s="3">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="D92" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A93" s="2">
+        <v>45719</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>19</v>
+      </c>
+      <c r="B94" s="3">
+        <v>0.4375</v>
+      </c>
+      <c r="C94" s="3">
+        <v>0.44791666666666669</v>
+      </c>
+      <c r="D94" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>19</v>
+      </c>
+      <c r="B95" s="3">
+        <v>0.44791666666666669</v>
+      </c>
+      <c r="C95" s="3">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D95" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>19</v>
+      </c>
+      <c r="B96" s="3">
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="C96" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="D96" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>19</v>
+      </c>
+      <c r="B97" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="C97" s="3">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="D97" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>19</v>
+      </c>
+      <c r="B98" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="C98" s="3">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="D98" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>21</v>
+      </c>
+      <c r="B99" s="3">
+        <v>0.625</v>
+      </c>
+      <c r="C99" s="3">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="D99" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>19</v>
+      </c>
+      <c r="B100" s="3">
+        <v>0.65625</v>
+      </c>
+      <c r="C100" s="3">
+        <v>0.67708333333333337</v>
+      </c>
+      <c r="D100" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A101" s="2">
+        <v>45720</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>19</v>
+      </c>
+      <c r="B102" s="3">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="C102" s="3">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D102" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>19</v>
+      </c>
+      <c r="B103" s="3">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="C103" s="3">
+        <v>0.36458333333333331</v>
+      </c>
+      <c r="D103" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>19</v>
+      </c>
+      <c r="B104" s="3">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="C104" s="3">
+        <v>0.36458333333333331</v>
+      </c>
+      <c r="D104" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>19</v>
+      </c>
+      <c r="B105" s="3">
+        <v>0.38541666666666669</v>
+      </c>
+      <c r="C105" s="3">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="D105" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>24</v>
+      </c>
+      <c r="B106" s="3">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="C106" s="3">
+        <v>0.4375</v>
+      </c>
+      <c r="D106" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>19</v>
+      </c>
+      <c r="B107" s="3">
+        <v>0.44791666666666669</v>
+      </c>
+      <c r="C107" s="3">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D107" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>19</v>
+      </c>
+      <c r="B108" s="3">
+        <v>0.55208333333333337</v>
+      </c>
+      <c r="C108" s="3">
+        <v>0.5625</v>
+      </c>
+      <c r="D108" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>19</v>
+      </c>
+      <c r="B109" s="3">
+        <v>0.55208333333333337</v>
+      </c>
+      <c r="C109" s="3">
+        <v>0.5625</v>
+      </c>
+      <c r="D109" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>19</v>
+      </c>
+      <c r="B110" s="3">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="C110" s="3">
+        <v>0.65625</v>
+      </c>
+      <c r="D110" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>19</v>
+      </c>
+      <c r="B111" s="3">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="C111" s="3">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="D111" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>34</v>
+      </c>
+      <c r="B112" s="3">
+        <v>0.67708333333333337</v>
+      </c>
+      <c r="C112" s="3">
+        <v>0.6875</v>
+      </c>
+      <c r="D112" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A113" s="2">
+        <v>45721</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>19</v>
+      </c>
+      <c r="B114" s="3">
+        <v>0.3125</v>
+      </c>
+      <c r="C114" s="3">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D114" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>19</v>
+      </c>
+      <c r="B115" s="3">
+        <v>0.32291666666666669</v>
+      </c>
+      <c r="C115" s="3">
+        <v>0.34375</v>
+      </c>
+      <c r="D115" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>19</v>
+      </c>
+      <c r="B116" s="3">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="C116" s="3">
+        <v>0.40625</v>
+      </c>
+      <c r="D116" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>19</v>
+      </c>
+      <c r="B117" s="3">
+        <v>0.44791666666666669</v>
+      </c>
+      <c r="C117" s="3">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D117" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>19</v>
+      </c>
+      <c r="B118" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="C118" s="3">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="D118" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>107</v>
+      </c>
+      <c r="B119" s="3">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="C119" s="3">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="D119" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>19</v>
+      </c>
+      <c r="B120" s="3">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="C120" s="3">
+        <v>0.59375</v>
+      </c>
+      <c r="D120" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>19</v>
+      </c>
+      <c r="B121" s="3">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="C121" s="3">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="D121" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>111</v>
+      </c>
+      <c r="B122" s="3">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="C122" s="3">
+        <v>0.6875</v>
+      </c>
+      <c r="D122" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A123" s="2">
+        <v>45722</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>19</v>
+      </c>
+      <c r="B124" s="3">
+        <v>0.3125</v>
+      </c>
+      <c r="C124" s="3">
+        <v>0.32291666666666669</v>
+      </c>
+      <c r="D124" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>19</v>
+      </c>
+      <c r="B125" s="3">
+        <v>0.32291666666666669</v>
+      </c>
+      <c r="C125" s="3">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D125" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>19</v>
+      </c>
+      <c r="B126" s="3">
+        <v>0.375</v>
+      </c>
+      <c r="C126" s="3">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="D126" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>19</v>
+      </c>
+      <c r="B127" s="3">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="C127" s="3">
+        <v>0.4375</v>
+      </c>
+      <c r="D127" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>19</v>
+      </c>
+      <c r="B128" s="3">
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="C128" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="D128" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="129" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>19</v>
+      </c>
+      <c r="B129" s="3">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="C129" s="3">
+        <v>0.51041666666666663</v>
+      </c>
+      <c r="D129" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="130" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>19</v>
+      </c>
+      <c r="B130" s="3">
+        <v>0.51041666666666663</v>
+      </c>
+      <c r="C130" s="3">
+        <v>0.61458333333333337</v>
+      </c>
+      <c r="D130" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="131" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>19</v>
+      </c>
+      <c r="B131" s="3">
+        <v>0.61458333333333337</v>
+      </c>
+      <c r="C131" s="3">
+        <v>0.625</v>
+      </c>
+      <c r="D131" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="132" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>19</v>
+      </c>
+      <c r="B132" s="3">
+        <v>0.625</v>
+      </c>
+      <c r="C132" s="3">
+        <v>0.63541666666666663</v>
+      </c>
+      <c r="D132" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="133" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>19</v>
+      </c>
+      <c r="B133" s="3">
+        <v>0.63541666666666663</v>
+      </c>
+      <c r="C133" s="3">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="D133" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="134" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>19</v>
+      </c>
+      <c r="B134" s="3">
+        <v>0.65625</v>
+      </c>
+      <c r="C134" s="3">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="D134" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="135" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>19</v>
+      </c>
+      <c r="B135" s="3">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="C135" s="3">
+        <v>0.6875</v>
+      </c>
+      <c r="D135" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="136" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>19</v>
+      </c>
+      <c r="B136" s="3">
+        <v>0.6875</v>
+      </c>
+      <c r="C136" s="3">
+        <v>0.69791666666666663</v>
+      </c>
+      <c r="D136" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="137" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A137" s="2">
+        <v>45723</v>
+      </c>
+    </row>
+    <row r="138" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>125</v>
+      </c>
+      <c r="B138" s="3">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="C138" s="3">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D138" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="139" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>19</v>
+      </c>
+      <c r="B139" s="3">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="C139" s="3">
+        <v>0.42708333333333331</v>
+      </c>
+      <c r="D139" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="140" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
+        <v>34</v>
+      </c>
+      <c r="B140" s="3">
+        <v>0.48958333333333331</v>
+      </c>
+      <c r="C140" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="D140" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="141" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
+        <v>19</v>
+      </c>
+      <c r="B141" s="3">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="C141" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="D141" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="142" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
+        <v>19</v>
+      </c>
+      <c r="B142" s="3">
+        <v>0.67708333333333337</v>
+      </c>
+      <c r="C142" s="3">
+        <v>0.69791666666666663</v>
+      </c>
+      <c r="D142" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="143" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A143" s="2">
+        <v>45726</v>
+      </c>
+    </row>
+    <row r="144" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A144" t="s">
+        <v>125</v>
+      </c>
+      <c r="B144" s="3">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="C144" s="3">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D144" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="145" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A145" t="s">
+        <v>19</v>
+      </c>
+      <c r="B145" s="3">
+        <v>0.36458333333333331</v>
+      </c>
+      <c r="C145" s="3">
+        <v>0.375</v>
+      </c>
+      <c r="D145" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="146" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A146" t="s">
+        <v>19</v>
+      </c>
+      <c r="B146" s="3">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="C146" s="3">
+        <v>0.42708333333333331</v>
+      </c>
+      <c r="D146" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="147" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
+        <v>125</v>
+      </c>
+      <c r="B147" s="3">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="C147" s="3">
+        <v>0.55208333333333337</v>
+      </c>
+      <c r="D147" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="148" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A148" s="2">
+        <v>45727</v>
+      </c>
+    </row>
+    <row r="149" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A149" t="s">
+        <v>19</v>
+      </c>
+      <c r="B149" s="3">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="C149" s="3">
+        <v>0.40625</v>
+      </c>
+      <c r="D149" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="150" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A150" t="s">
+        <v>34</v>
+      </c>
+      <c r="B150" s="3">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="C150" s="3">
+        <v>0.40625</v>
+      </c>
+      <c r="D150" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="151" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A151" t="s">
+        <v>137</v>
+      </c>
+      <c r="B151" s="3">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="C151" s="3">
+        <v>0.42708333333333331</v>
+      </c>
+      <c r="D151" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="152" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A152" t="s">
+        <v>19</v>
+      </c>
+      <c r="B152" s="3">
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="C152" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="D152" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="153" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A153" t="s">
+        <v>19</v>
+      </c>
+      <c r="B153" s="3">
+        <v>0.40625</v>
+      </c>
+      <c r="C153" s="3">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D153" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="154" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A154" t="s">
+        <v>19</v>
+      </c>
+      <c r="B154" s="3">
+        <v>0.51041666666666663</v>
+      </c>
+      <c r="C154" s="3">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="D154" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="155" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A155" t="s">
+        <v>19</v>
+      </c>
+      <c r="B155" s="3">
+        <v>0.53125</v>
+      </c>
+      <c r="C155" s="3">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="D155" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="156" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A156" t="s">
+        <v>137</v>
+      </c>
+      <c r="B156" s="3">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="C156" s="3">
+        <v>0.55208333333333337</v>
+      </c>
+      <c r="D156" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="157" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A157" t="s">
+        <v>143</v>
+      </c>
+      <c r="B157" s="3">
+        <v>0.55208333333333337</v>
+      </c>
+      <c r="C157" s="3">
+        <v>0.5625</v>
+      </c>
+      <c r="D157" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="158" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A158" t="s">
+        <v>19</v>
+      </c>
+      <c r="B158" s="3">
+        <v>0.59375</v>
+      </c>
+      <c r="C158" s="3">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="D158" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="159" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A159" t="s">
+        <v>19</v>
+      </c>
+      <c r="B159" s="3">
+        <v>0.61458333333333337</v>
+      </c>
+      <c r="C159" s="3">
+        <v>0.65625</v>
+      </c>
+      <c r="D159" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="160" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A160" s="2">
+        <v>45728</v>
+      </c>
+    </row>
+    <row r="161" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A161" t="s">
+        <v>19</v>
+      </c>
+      <c r="B161" s="3">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="C161" s="3">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D161" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="162" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A162" t="s">
+        <v>19</v>
+      </c>
+      <c r="B162" s="3">
+        <v>0.4375</v>
+      </c>
+      <c r="C162" s="3">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D162" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="163" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A163" t="s">
+        <v>19</v>
+      </c>
+      <c r="B163" s="3">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="C163" s="3">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="D163" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="164" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A164" t="s">
+        <v>19</v>
+      </c>
+      <c r="B164" s="3">
+        <v>0.55208333333333337</v>
+      </c>
+      <c r="C164" s="3">
+        <v>0.5625</v>
+      </c>
+      <c r="D164" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="165" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A165" t="s">
+        <v>150</v>
+      </c>
+      <c r="B165" s="3">
+        <v>0.5625</v>
+      </c>
+      <c r="C165" s="3">
+        <v>0.6875</v>
+      </c>
+      <c r="D165" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="166" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A166" s="2">
+        <v>45729</v>
+      </c>
+    </row>
+    <row r="167" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A167" t="s">
+        <v>34</v>
+      </c>
+      <c r="B167" s="3">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="C167" s="3">
+        <v>0.375</v>
+      </c>
+      <c r="D167" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="168" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A168" t="s">
+        <v>19</v>
+      </c>
+      <c r="B168" s="3">
+        <v>0.375</v>
+      </c>
+      <c r="C168" s="3">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="D168" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="169" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A169" t="s">
+        <v>19</v>
+      </c>
+      <c r="B169" s="3">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="C169" s="3">
+        <v>0.4375</v>
+      </c>
+      <c r="D169" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="170" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A170" t="s">
+        <v>24</v>
+      </c>
+      <c r="B170" s="3">
+        <v>0.4375</v>
+      </c>
+      <c r="C170" s="3">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="D170" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="171" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A171" t="s">
+        <v>137</v>
+      </c>
+      <c r="B171" s="3">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="C171" s="3">
+        <v>0.46875</v>
+      </c>
+      <c r="D171" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="172" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A172" t="s">
+        <v>19</v>
+      </c>
+      <c r="B172" s="3">
+        <v>0.53125</v>
+      </c>
+      <c r="C172" s="3">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="D172" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="173" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A173" t="s">
+        <v>24</v>
+      </c>
+      <c r="B173" s="3">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="C173" s="3">
+        <v>0.5625</v>
+      </c>
+      <c r="D173" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="174" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A174" t="s">
+        <v>34</v>
+      </c>
+      <c r="B174" s="3">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="C174" s="3">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D174" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="175" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A175" t="s">
+        <v>19</v>
+      </c>
+      <c r="B175" s="3">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="C175" s="3">
+        <v>0.61458333333333337</v>
+      </c>
+      <c r="D175" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="176" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A176" s="2">
+        <v>45730</v>
+      </c>
+    </row>
+    <row r="177" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A177" t="s">
+        <v>137</v>
+      </c>
+      <c r="B177" s="3">
+        <v>0.36458333333333331</v>
+      </c>
+      <c r="C177" s="3">
+        <v>0.375</v>
+      </c>
+      <c r="D177" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="178" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A178" t="s">
+        <v>19</v>
+      </c>
+      <c r="B178" s="3">
+        <v>0.375</v>
+      </c>
+      <c r="C178" s="3">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="D178" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="179" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A179" t="s">
+        <v>19</v>
+      </c>
+      <c r="B179" s="3">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="C179" s="3">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="D179" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="180" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A180" t="s">
+        <v>19</v>
+      </c>
+      <c r="B180" s="3">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="C180" s="3">
+        <v>0.55208333333333337</v>
+      </c>
+      <c r="D180" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="181" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A181" t="s">
+        <v>19</v>
+      </c>
+      <c r="B181" s="3">
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="C181" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="D181" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="182" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A182" s="2">
+        <v>45732</v>
+      </c>
+    </row>
+    <row r="183" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A183" t="s">
+        <v>19</v>
+      </c>
+      <c r="B183" s="3">
+        <v>0.36458333333333331</v>
+      </c>
+      <c r="C183" s="3">
+        <v>0.375</v>
+      </c>
+      <c r="D183" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="184" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A184" s="2">
+        <v>45733</v>
+      </c>
+    </row>
+    <row r="185" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A185" t="s">
+        <v>19</v>
+      </c>
+      <c r="B185" s="3">
+        <v>0.36458333333333331</v>
+      </c>
+      <c r="C185" s="3">
+        <v>0.375</v>
+      </c>
+      <c r="D185" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="186" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A186" t="s">
+        <v>19</v>
+      </c>
+      <c r="B186" s="3">
+        <v>0.375</v>
+      </c>
+      <c r="C186" s="3">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="D186" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="187" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A187" t="s">
+        <v>19</v>
+      </c>
+      <c r="B187" s="3">
+        <v>0.40625</v>
+      </c>
+      <c r="C187" s="3">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D187" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="188" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A188" t="s">
+        <v>19</v>
+      </c>
+      <c r="B188" s="3">
+        <v>0.44791666666666669</v>
+      </c>
+      <c r="C188" s="3">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D188" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="189" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A189" t="s">
+        <v>19</v>
+      </c>
+      <c r="B189" s="3">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="C189" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="D189" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="190" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A190" t="s">
+        <v>19</v>
+      </c>
+      <c r="B190" s="3">
+        <v>0.55208333333333337</v>
+      </c>
+      <c r="C190" s="3">
+        <v>0.5625</v>
+      </c>
+      <c r="D190" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="191" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A191" t="s">
+        <v>19</v>
+      </c>
+      <c r="B191" s="3">
+        <v>0.61458333333333337</v>
+      </c>
+      <c r="C191" s="3">
+        <v>0.625</v>
+      </c>
+      <c r="D191" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="192" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A192" s="2">
+        <v>45734</v>
+      </c>
+    </row>
+    <row r="193" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A193" t="s">
+        <v>19</v>
+      </c>
+      <c r="B193" s="3">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="C193" s="3">
+        <v>0.34375</v>
+      </c>
+      <c r="D193" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="194" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A194" t="s">
+        <v>19</v>
+      </c>
+      <c r="B194" s="3">
+        <v>0.34375</v>
+      </c>
+      <c r="C194" s="3">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D194" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="195" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A195" t="s">
+        <v>19</v>
+      </c>
+      <c r="B195" s="3">
+        <v>0.36458333333333331</v>
+      </c>
+      <c r="C195" s="3">
+        <v>0.375</v>
+      </c>
+      <c r="D195" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="196" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A196" t="s">
+        <v>19</v>
+      </c>
+      <c r="B196" s="3">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="C196" s="3">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D196" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="197" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A197" t="s">
+        <v>19</v>
+      </c>
+      <c r="B197" s="3">
+        <v>0.44791666666666669</v>
+      </c>
+      <c r="C197" s="3">
+        <v>0.46875</v>
+      </c>
+      <c r="D197" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="198" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A198" t="s">
+        <v>174</v>
+      </c>
+      <c r="B198" s="3">
+        <v>0.46875</v>
+      </c>
+      <c r="C198" s="3">
+        <v>0.6875</v>
+      </c>
+      <c r="D198" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="199" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A199" s="2">
+        <v>45735</v>
+      </c>
+    </row>
+    <row r="200" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A200" t="s">
+        <v>19</v>
+      </c>
+      <c r="B200" s="3">
+        <v>0.32291666666666669</v>
+      </c>
+      <c r="C200" s="3">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D200" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="201" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A201" t="s">
+        <v>19</v>
+      </c>
+      <c r="B201" s="3">
+        <v>0.32291666666666669</v>
+      </c>
+      <c r="C201" s="3">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D201" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="202" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A202" t="s">
+        <v>19</v>
+      </c>
+      <c r="B202" s="3">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="C202" s="3">
+        <v>0.34166666666666662</v>
+      </c>
+      <c r="D202" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="203" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A203" t="s">
+        <v>174</v>
+      </c>
+      <c r="B203" s="3">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="C203" s="3">
+        <v>0.6875</v>
+      </c>
+      <c r="D203" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="204" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A204" t="s">
+        <v>19</v>
+      </c>
+      <c r="B204" s="3">
+        <v>0.34375</v>
+      </c>
+      <c r="C204" s="3">
+        <v>0.375</v>
+      </c>
+      <c r="D204" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="205" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A205" t="s">
+        <v>19</v>
+      </c>
+      <c r="B205" s="3">
+        <v>0.40625</v>
+      </c>
+      <c r="C205" s="3">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D205" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="206" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A206" t="s">
+        <v>19</v>
+      </c>
+      <c r="B206" s="3">
+        <v>0.4375</v>
+      </c>
+      <c r="C206" s="3">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D206" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="207" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A207" t="s">
+        <v>19</v>
+      </c>
+      <c r="B207" s="3">
+        <v>0.48958333333333331</v>
+      </c>
+      <c r="C207" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="D207" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="208" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A208" t="s">
+        <v>19</v>
+      </c>
+      <c r="B208" s="3">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="C208" s="3">
+        <v>0.5625</v>
+      </c>
+      <c r="D208" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="209" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A209" t="s">
+        <v>19</v>
+      </c>
+      <c r="B209" s="3">
+        <v>0.5625</v>
+      </c>
+      <c r="C209" s="3">
+        <v>0.57291666666666663</v>
+      </c>
+      <c r="D209" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="210" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A210" t="s">
+        <v>19</v>
+      </c>
+      <c r="B210" s="3">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="C210" s="3">
+        <v>0.6875</v>
+      </c>
+      <c r="D210" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="211" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A211" t="s">
+        <v>19</v>
+      </c>
+      <c r="B211" s="3">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="C211" s="3">
+        <v>0.6875</v>
+      </c>
+      <c r="D211" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="212" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A212" t="s">
+        <v>19</v>
+      </c>
+      <c r="B212" s="3">
+        <v>0.6875</v>
+      </c>
+      <c r="C212" s="3">
+        <v>0.69791666666666663</v>
+      </c>
+      <c r="D212" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="213" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A213" s="2">
+        <v>45736</v>
+      </c>
+    </row>
+    <row r="214" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A214" t="s">
+        <v>19</v>
+      </c>
+      <c r="B214" s="3">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="C214" s="3">
+        <v>0.375</v>
+      </c>
+      <c r="D214" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="215" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A215" t="s">
+        <v>19</v>
+      </c>
+      <c r="B215" s="3">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="C215" s="3">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D215" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="216" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A216" t="s">
+        <v>19</v>
+      </c>
+      <c r="B216" s="3">
+        <v>0.46875</v>
+      </c>
+      <c r="C216" s="3">
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="D216" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="217" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A217" t="s">
+        <v>19</v>
+      </c>
+      <c r="B217" s="3">
+        <v>0.65625</v>
+      </c>
+      <c r="C217" s="3">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="D217" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="218" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A218" s="2">
+        <v>45740</v>
+      </c>
+    </row>
+    <row r="219" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A219" t="s">
+        <v>19</v>
+      </c>
+      <c r="B219" s="3">
+        <v>0.34375</v>
+      </c>
+      <c r="C219" s="3">
+        <v>0.375</v>
+      </c>
+      <c r="D219" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="220" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A220" t="s">
+        <v>19</v>
+      </c>
+      <c r="B220" s="3">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="C220" s="3">
+        <v>0.4375</v>
+      </c>
+      <c r="D220" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="221" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A221" t="s">
+        <v>24</v>
+      </c>
+      <c r="B221" s="3">
+        <v>0.4375</v>
+      </c>
+      <c r="C221" s="3">
+        <v>0.46875</v>
+      </c>
+      <c r="D221" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="222" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A222" t="s">
+        <v>19</v>
+      </c>
+      <c r="B222" s="3">
+        <v>0.46875</v>
+      </c>
+      <c r="C222" s="3">
+        <v>0.48958333333333331</v>
+      </c>
+      <c r="D222" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="223" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A223" t="s">
+        <v>19</v>
+      </c>
+      <c r="B223" s="3">
+        <v>0.625</v>
+      </c>
+      <c r="C223" s="3">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="D223" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="224" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A224" t="s">
+        <v>19</v>
+      </c>
+      <c r="B224" s="3">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="C224" s="3">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="D224" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="225" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A225" s="2">
+        <v>45741</v>
+      </c>
+    </row>
+    <row r="226" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A226" t="s">
+        <v>19</v>
+      </c>
+      <c r="B226" s="3">
+        <v>0.34375</v>
+      </c>
+      <c r="C226" s="3">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D226" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="227" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A227" t="s">
+        <v>19</v>
+      </c>
+      <c r="B227" s="3">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="C227" s="3">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D227" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="228" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A228" t="s">
+        <v>19</v>
+      </c>
+      <c r="B228" s="3">
+        <v>0.44791666666666669</v>
+      </c>
+      <c r="C228" s="3">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D228" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="229" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A229" t="s">
+        <v>19</v>
+      </c>
+      <c r="B229" s="3">
+        <v>0.46875</v>
+      </c>
+      <c r="C229" s="3">
+        <v>0.48958333333333331</v>
+      </c>
+      <c r="D229" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="230" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A230" t="s">
+        <v>137</v>
+      </c>
+      <c r="B230" s="3">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="C230" s="3">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D230" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="231" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A231" s="2">
+        <v>45742</v>
+      </c>
+    </row>
+    <row r="232" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A232" t="s">
+        <v>19</v>
+      </c>
+      <c r="B232" s="3">
+        <v>0.375</v>
+      </c>
+      <c r="C232" s="3">
+        <v>0.38541666666666669</v>
+      </c>
+      <c r="D232" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="233" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A233" t="s">
+        <v>19</v>
+      </c>
+      <c r="B233" s="3">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="C233" s="3">
+        <v>0.40625</v>
+      </c>
+      <c r="D233" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="234" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A234" t="s">
+        <v>19</v>
+      </c>
+      <c r="B234" s="3">
+        <v>0.42708333333333331</v>
+      </c>
+      <c r="C234" s="3">
+        <v>0.4375</v>
+      </c>
+      <c r="D234" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="235" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A235" t="s">
+        <v>19</v>
+      </c>
+      <c r="B235" s="3">
+        <v>0.4375</v>
+      </c>
+      <c r="C235" s="3">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D235" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="236" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A236" t="s">
+        <v>19</v>
+      </c>
+      <c r="B236" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="C236" s="3">
+        <v>0.51041666666666663</v>
+      </c>
+      <c r="D236" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="237" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A237" t="s">
+        <v>19</v>
+      </c>
+      <c r="B237" s="3">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="C237" s="3">
+        <v>0.6875</v>
+      </c>
+      <c r="D237" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="238" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A238" t="s">
+        <v>19</v>
+      </c>
+      <c r="B238" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="C238" s="3">
+        <v>0.625</v>
+      </c>
+      <c r="D238" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="239" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A239" s="2">
+        <v>45743</v>
+      </c>
+    </row>
+    <row r="240" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A240" t="s">
+        <v>19</v>
+      </c>
+      <c r="B240" s="3">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="C240" s="3">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D240" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="241" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A241" t="s">
+        <v>19</v>
+      </c>
+      <c r="B241" s="3">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="C241" s="3">
+        <v>0.42708333333333331</v>
+      </c>
+      <c r="D241" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="242" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A242" t="s">
+        <v>19</v>
+      </c>
+      <c r="B242" s="3">
+        <v>0.42708333333333331</v>
+      </c>
+      <c r="C242" s="3">
+        <v>0.4375</v>
+      </c>
+      <c r="D242" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="243" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A243" t="s">
+        <v>19</v>
+      </c>
+      <c r="B243" s="3">
+        <v>0.4375</v>
+      </c>
+      <c r="C243" s="3">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D243" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="244" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A244" t="s">
+        <v>19</v>
+      </c>
+      <c r="B244" s="3">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="C244" s="3">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="D244" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="245" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A245" t="s">
+        <v>19</v>
+      </c>
+      <c r="B245" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="C245" s="3">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="D245" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="246" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A246" t="s">
+        <v>19</v>
+      </c>
+      <c r="B246" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="C246" s="3">
+        <v>0.51041666666666663</v>
+      </c>
+      <c r="D246" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="247" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A247" t="s">
+        <v>19</v>
+      </c>
+      <c r="B247" s="3">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="C247" s="3">
+        <v>0.59375</v>
+      </c>
+      <c r="D247" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="248" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A248" t="s">
+        <v>34</v>
+      </c>
+      <c r="B248" s="3">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="C248" s="3">
+        <v>0.61458333333333337</v>
+      </c>
+      <c r="D248" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="249" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A249" s="2">
+        <v>45744</v>
+      </c>
+    </row>
+    <row r="250" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A250" t="s">
+        <v>125</v>
+      </c>
+      <c r="B250" s="3">
+        <v>0.3125</v>
+      </c>
+      <c r="C250" s="3">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D250" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="251" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A251" t="s">
+        <v>218</v>
+      </c>
+      <c r="B251" s="3">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="C251" s="3">
+        <v>0.36458333333333331</v>
+      </c>
+      <c r="D251" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="252" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A252" t="s">
+        <v>220</v>
+      </c>
+      <c r="B252" s="3">
+        <v>0.375</v>
+      </c>
+      <c r="C252" s="3">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D252" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="253" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A253" t="s">
+        <v>125</v>
+      </c>
+      <c r="B253" s="3">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="C253" s="3">
+        <v>0.4375</v>
+      </c>
+      <c r="D253" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="254" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A254" t="s">
+        <v>24</v>
+      </c>
+      <c r="B254" s="3">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="C254" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="D254" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="255" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A255" t="s">
+        <v>19</v>
+      </c>
+      <c r="B255" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="C255" s="3">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="D255" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="256" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A256" s="2">
+        <v>45747</v>
+      </c>
+    </row>
+    <row r="257" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A257" t="s">
+        <v>19</v>
+      </c>
+      <c r="B257" s="3">
+        <v>0.36458333333333331</v>
+      </c>
+      <c r="C257" s="3">
+        <v>0.375</v>
+      </c>
+      <c r="D257" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="258" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A258" t="s">
+        <v>19</v>
+      </c>
+      <c r="B258" s="3">
+        <v>0.375</v>
+      </c>
+      <c r="C258" s="3">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="D258" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="259" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A259" t="s">
+        <v>19</v>
+      </c>
+      <c r="B259" s="3">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="C259" s="3">
+        <v>0.40625</v>
+      </c>
+      <c r="D259" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="260" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A260" t="s">
+        <v>19</v>
+      </c>
+      <c r="B260" s="3">
+        <v>0.40625</v>
+      </c>
+      <c r="C260" s="3">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D260" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="261" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A261" t="s">
+        <v>19</v>
+      </c>
+      <c r="B261" s="3">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="C261" s="3">
+        <v>0.4375</v>
+      </c>
+      <c r="D261" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="262" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A262" t="s">
+        <v>19</v>
+      </c>
+      <c r="B262" s="3">
+        <v>0.4375</v>
+      </c>
+      <c r="C262" s="3">
+        <v>0.44791666666666669</v>
+      </c>
+      <c r="D262" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="263" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A263" t="s">
+        <v>19</v>
+      </c>
+      <c r="B263" s="3">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="C263" s="3">
+        <v>0.46875</v>
+      </c>
+      <c r="D263" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="264" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A264" t="s">
+        <v>19</v>
+      </c>
+      <c r="B264" s="3">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="C264" s="3">
+        <v>0.46875</v>
+      </c>
+      <c r="D264" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="265" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A265" t="s">
+        <v>19</v>
+      </c>
+      <c r="B265" s="3">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="C265" s="3">
+        <v>0.53125</v>
+      </c>
+      <c r="D265" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="266" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A266" t="s">
+        <v>19</v>
+      </c>
+      <c r="B266" s="3">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="C266" s="3">
+        <v>0.53125</v>
+      </c>
+      <c r="D266" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="267" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A267" s="2">
+        <v>45748</v>
+      </c>
+    </row>
+    <row r="268" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A268" t="s">
+        <v>19</v>
+      </c>
+      <c r="B268" s="3">
+        <v>0.34375</v>
+      </c>
+      <c r="C268" s="3">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D268" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="269" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A269" t="s">
+        <v>19</v>
+      </c>
+      <c r="B269" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="C269" s="3">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="D269" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="270" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A270" t="s">
+        <v>19</v>
+      </c>
+      <c r="B270" s="3">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="C270" s="3">
+        <v>0.55208333333333337</v>
+      </c>
+      <c r="D270" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="271" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A271" t="s">
+        <v>19</v>
+      </c>
+      <c r="B271" s="3">
+        <v>0.55208333333333337</v>
+      </c>
+      <c r="C271" s="3">
+        <v>0.57291666666666663</v>
+      </c>
+      <c r="D271" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="272" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A272" t="s">
+        <v>34</v>
+      </c>
+      <c r="B272" s="3">
+        <v>0.57291666666666663</v>
+      </c>
+      <c r="C272" s="3">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D272" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="273" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A273" t="s">
+        <v>19</v>
+      </c>
+      <c r="B273" s="3">
+        <v>0.61458333333333337</v>
+      </c>
+      <c r="C273" s="3">
+        <v>0.625</v>
+      </c>
+      <c r="D273" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="274" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A274" t="s">
+        <v>235</v>
+      </c>
+      <c r="B274" s="3">
+        <v>0.625</v>
+      </c>
+      <c r="C274" s="3">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="D274" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="275" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A275" s="2">
+        <v>45749</v>
+      </c>
+    </row>
+    <row r="276" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A276" t="s">
+        <v>19</v>
+      </c>
+      <c r="B276" s="3">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="C276" s="3">
+        <v>0.34375</v>
+      </c>
+      <c r="D276" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="277" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A277" t="s">
+        <v>19</v>
+      </c>
+      <c r="B277" s="3">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="C277" s="3">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D277" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="278" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A278" t="s">
+        <v>34</v>
+      </c>
+      <c r="B278" s="3">
+        <v>0.48958333333333331</v>
+      </c>
+      <c r="C278" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="D278" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="279" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A279" t="s">
+        <v>19</v>
+      </c>
+      <c r="B279" s="3">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="C279" s="3">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="D279" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="280" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A280" t="s">
+        <v>19</v>
+      </c>
+      <c r="B280" s="3">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="C280" s="3">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D280" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="281" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A281" t="s">
+        <v>19</v>
+      </c>
+      <c r="B281" s="3">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="C281" s="3">
+        <v>0.61458333333333337</v>
+      </c>
+      <c r="D281" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="282" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A282" t="s">
+        <v>19</v>
+      </c>
+      <c r="B282" s="3">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="C282" s="3">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="D282" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="283" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A283" t="s">
+        <v>19</v>
+      </c>
+      <c r="B283" s="3">
+        <v>0.625</v>
+      </c>
+      <c r="C283" s="3">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="D283" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="284" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A284" t="s">
+        <v>19</v>
+      </c>
+      <c r="B284" s="3">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="C284" s="3">
+        <v>0.69444444444444453</v>
+      </c>
+      <c r="D284" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="285" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A285" s="2">
+        <v>45750</v>
+      </c>
+    </row>
+    <row r="286" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A286" t="s">
+        <v>19</v>
+      </c>
+      <c r="B286" s="3">
+        <v>0.36458333333333331</v>
+      </c>
+      <c r="C286" s="3">
+        <v>0.375</v>
+      </c>
+      <c r="D286" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="287" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A287" t="s">
+        <v>19</v>
+      </c>
+      <c r="B287" s="3">
+        <v>0.4375</v>
+      </c>
+      <c r="C287" s="3">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D287" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="288" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A288" t="s">
+        <v>125</v>
+      </c>
+      <c r="B288" s="3">
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="C288" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="D288" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="289" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A289" t="s">
+        <v>19</v>
+      </c>
+      <c r="B289" s="3">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="C289" s="3">
+        <v>0.5625</v>
+      </c>
+      <c r="D289" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="290" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A290" t="s">
+        <v>245</v>
+      </c>
+      <c r="B290" s="3">
+        <v>0.5625</v>
+      </c>
+      <c r="C290" s="3">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D290" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="291" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A291" t="s">
+        <v>19</v>
+      </c>
+      <c r="B291" s="3">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="C291" s="3">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="D291" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="292" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A292" s="2">
+        <v>45751</v>
+      </c>
+    </row>
+    <row r="293" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A293" t="s">
+        <v>19</v>
+      </c>
+      <c r="B293" s="3">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="C293" s="3">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D293" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="294" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A294" t="s">
+        <v>19</v>
+      </c>
+      <c r="B294" s="3">
+        <v>0.44791666666666669</v>
+      </c>
+      <c r="C294" s="3">
+        <v>0.46875</v>
+      </c>
+      <c r="D294" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="295" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A295" t="s">
+        <v>19</v>
+      </c>
+      <c r="B295" s="3">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="C295" s="3">
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="D295" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="296" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A296" t="s">
+        <v>19</v>
+      </c>
+      <c r="B296" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="C296" s="3">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="D296" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="297" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A297" t="s">
+        <v>19</v>
+      </c>
+      <c r="B297" s="3">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="C297" s="3">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="D297" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="298" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A298" t="s">
+        <v>19</v>
+      </c>
+      <c r="B298" s="3">
+        <v>0.625</v>
+      </c>
+      <c r="C298" s="3">
+        <v>0.63541666666666663</v>
+      </c>
+      <c r="D298" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="299" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A299" s="2">
+        <v>45754</v>
+      </c>
+    </row>
+    <row r="300" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A300" t="s">
+        <v>34</v>
+      </c>
+      <c r="B300" s="3">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="C300" s="3">
+        <v>0.375</v>
+      </c>
+      <c r="D300" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="301" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A301" t="s">
+        <v>19</v>
+      </c>
+      <c r="B301" s="3">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="C301" s="3">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D301" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="302" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A302" t="s">
+        <v>19</v>
+      </c>
+      <c r="B302" s="3">
+        <v>0.48958333333333331</v>
+      </c>
+      <c r="C302" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="D302" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="303" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A303" t="s">
+        <v>19</v>
+      </c>
+      <c r="B303" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="C303" s="3">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="D303" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="304" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A304" t="s">
+        <v>19</v>
+      </c>
+      <c r="B304" s="3">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="C304" s="3">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="D304" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="305" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A305" t="s">
+        <v>19</v>
+      </c>
+      <c r="B305" s="3">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="C305" s="3">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="D305" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="306" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A306" t="s">
+        <v>34</v>
+      </c>
+      <c r="B306" s="3">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="C306" s="3">
+        <v>0.6875</v>
+      </c>
+      <c r="D306" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="307" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A307" s="2">
+        <v>45755</v>
+      </c>
+    </row>
+    <row r="308" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A308" t="s">
+        <v>19</v>
+      </c>
+      <c r="B308" s="3">
+        <v>0.34375</v>
+      </c>
+      <c r="C308" s="3">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D308" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="309" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A309" t="s">
+        <v>19</v>
+      </c>
+      <c r="B309" s="3">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="C309" s="3">
+        <v>0.36458333333333331</v>
+      </c>
+      <c r="D309" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="310" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A310" t="s">
+        <v>19</v>
+      </c>
+      <c r="B310" s="3">
+        <v>0.375</v>
+      </c>
+      <c r="C310" s="3">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="D310" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="311" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A311" t="s">
+        <v>34</v>
+      </c>
+      <c r="B311" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="C311" s="3">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="D311" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="312" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A312" t="s">
+        <v>19</v>
+      </c>
+      <c r="B312" s="3">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="C312" s="3">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="D312" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="313" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A313" t="s">
+        <v>137</v>
+      </c>
+      <c r="B313" s="3">
+        <v>0.55208333333333337</v>
+      </c>
+      <c r="C313" s="3">
+        <v>0.5625</v>
+      </c>
+      <c r="D313" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="314" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A314" t="s">
+        <v>19</v>
+      </c>
+      <c r="B314" s="3">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="C314" s="3">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="D314" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="315" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A315" t="s">
+        <v>19</v>
+      </c>
+      <c r="B315" s="3">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="C315" s="3">
+        <v>0.625</v>
+      </c>
+      <c r="D315" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="316" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A316" t="s">
+        <v>245</v>
+      </c>
+      <c r="B316" s="3">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="C316" s="3">
+        <v>0.625</v>
+      </c>
+      <c r="D316" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="317" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A317" t="s">
+        <v>19</v>
+      </c>
+      <c r="B317" s="3">
+        <v>0.625</v>
+      </c>
+      <c r="C317" s="3">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="D317" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="318" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A318" t="s">
+        <v>19</v>
+      </c>
+      <c r="B318" s="3">
+        <v>0.34375</v>
+      </c>
+      <c r="C318" s="3">
+        <v>0.6875</v>
+      </c>
+      <c r="D318" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="319" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A319" t="s">
+        <v>19</v>
+      </c>
+      <c r="B319" s="3">
+        <v>0.67708333333333337</v>
+      </c>
+      <c r="C319" s="3">
+        <v>0.6875</v>
+      </c>
+      <c r="D319" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="320" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A320" s="2">
+        <v>45756</v>
+      </c>
+    </row>
+    <row r="321" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A321" t="s">
+        <v>19</v>
+      </c>
+      <c r="B321" s="3">
+        <v>0.34375</v>
+      </c>
+      <c r="C321" s="3">
+        <v>0.6875</v>
+      </c>
+      <c r="D321" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="322" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A322" t="s">
+        <v>19</v>
+      </c>
+      <c r="B322" s="3">
+        <v>0.38541666666666669</v>
+      </c>
+      <c r="C322" s="3">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="D322" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="323" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A323" t="s">
+        <v>270</v>
+      </c>
+      <c r="B323" s="3">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="C323" s="3">
+        <v>0.6875</v>
+      </c>
+      <c r="D323" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="324" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A324" t="s">
+        <v>19</v>
+      </c>
+      <c r="B324" s="3">
+        <v>0.38541666666666669</v>
+      </c>
+      <c r="C324" s="3">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="D324" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="325" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A325" s="2">
+        <v>45757</v>
+      </c>
+    </row>
+    <row r="326" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A326" t="s">
+        <v>19</v>
+      </c>
+      <c r="B326" s="3">
+        <v>0.375</v>
+      </c>
+      <c r="C326" s="3">
+        <v>0.38541666666666669</v>
+      </c>
+      <c r="D326" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="327" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A327" t="s">
+        <v>270</v>
+      </c>
+      <c r="B327" s="3">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="C327" s="3">
+        <v>0.5625</v>
+      </c>
+      <c r="D327" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="328" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A328" t="s">
+        <v>19</v>
+      </c>
+      <c r="B328" s="3">
+        <v>0.59375</v>
+      </c>
+      <c r="C328" s="3">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="D328" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="329" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A329" t="s">
+        <v>34</v>
+      </c>
+      <c r="B329" s="3">
+        <v>0.59375</v>
+      </c>
+      <c r="C329" s="3">
+        <v>0.61458333333333337</v>
+      </c>
+      <c r="D329" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="330" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A330" t="s">
+        <v>137</v>
+      </c>
+      <c r="B330" s="3">
+        <v>0.65625</v>
+      </c>
+      <c r="C330" s="3">
+        <v>0.67708333333333337</v>
+      </c>
+      <c r="D330" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="331" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A331" t="s">
+        <v>19</v>
+      </c>
+      <c r="B331" s="3">
+        <v>0.67708333333333337</v>
+      </c>
+      <c r="C331" s="3">
+        <v>0.6875</v>
+      </c>
+      <c r="D331" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="332" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A332" s="2">
+        <v>45758</v>
+      </c>
+    </row>
+    <row r="333" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A333" t="s">
+        <v>19</v>
+      </c>
+      <c r="B333" s="3">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="C333" s="3">
+        <v>0.4375</v>
+      </c>
+      <c r="D333" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="334" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A334" t="s">
+        <v>34</v>
+      </c>
+      <c r="B334" s="3">
+        <v>0.4375</v>
+      </c>
+      <c r="C334" s="3">
+        <v>0.44791666666666669</v>
+      </c>
+      <c r="D334" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="335" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A335" t="s">
+        <v>19</v>
+      </c>
+      <c r="B335" s="3">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="C335" s="3">
+        <v>0.59375</v>
+      </c>
+      <c r="D335" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="336" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A336" s="2">
+        <v>45759</v>
+      </c>
+    </row>
+    <row r="337" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A337" t="s">
+        <v>19</v>
+      </c>
+      <c r="B337" s="3">
+        <v>0.30208333333333331</v>
+      </c>
+      <c r="C337" s="3">
+        <v>0.3125</v>
+      </c>
+      <c r="D337" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="338" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A338" s="2">
+        <v>45761</v>
+      </c>
+    </row>
+    <row r="339" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A339" t="s">
+        <v>19</v>
+      </c>
+      <c r="B339" s="3">
+        <v>0.34375</v>
+      </c>
+      <c r="C339" s="3">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D339" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="340" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A340" t="s">
+        <v>19</v>
+      </c>
+      <c r="B340" s="3">
+        <v>0.46875</v>
+      </c>
+      <c r="C340" s="3">
+        <v>0.48958333333333331</v>
+      </c>
+      <c r="D340" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="341" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A341" t="s">
+        <v>19</v>
+      </c>
+      <c r="B341" s="3">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="C341" s="3">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="D341" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="342" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A342" t="s">
+        <v>34</v>
+      </c>
+      <c r="B342" s="3">
+        <v>0.57291666666666663</v>
+      </c>
+      <c r="C342" s="3">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="D342" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="343" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A343" t="s">
+        <v>19</v>
+      </c>
+      <c r="B343" s="3">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="C343" s="3">
+        <v>0.6875</v>
+      </c>
+      <c r="D343" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="344" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A344" s="2">
+        <v>45762</v>
+      </c>
+    </row>
+    <row r="345" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A345" t="s">
+        <v>137</v>
+      </c>
+      <c r="B345" s="3">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="C345" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="D345" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="346" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A346" t="s">
+        <v>19</v>
+      </c>
+      <c r="B346" s="3">
+        <v>0.34375</v>
+      </c>
+      <c r="C346" s="3">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D346" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="347" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A347" t="s">
+        <v>19</v>
+      </c>
+      <c r="B347" s="3">
+        <v>0.38541666666666669</v>
+      </c>
+      <c r="C347" s="3">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="D347" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="348" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A348" t="s">
+        <v>19</v>
+      </c>
+      <c r="B348" s="3">
+        <v>0.38541666666666669</v>
+      </c>
+      <c r="C348" s="3">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="D348" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="349" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A349" t="s">
+        <v>19</v>
+      </c>
+      <c r="B349" s="3">
+        <v>0.40625</v>
+      </c>
+      <c r="C349" s="3">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D349" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="350" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A350" t="s">
+        <v>19</v>
+      </c>
+      <c r="B350" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="C350" s="3">
+        <v>0.51041666666666663</v>
+      </c>
+      <c r="D350" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="351" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A351" t="s">
+        <v>19</v>
+      </c>
+      <c r="B351" s="3">
+        <v>0.625</v>
+      </c>
+      <c r="C351" s="3">
+        <v>0.63541666666666663</v>
+      </c>
+      <c r="D351" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="352" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A352" s="2">
+        <v>45763</v>
+      </c>
+    </row>
+    <row r="353" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A353" t="s">
+        <v>34</v>
+      </c>
+      <c r="B353" s="3">
+        <v>0.32291666666666669</v>
+      </c>
+      <c r="C353" s="3">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D353" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="354" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A354" t="s">
+        <v>19</v>
+      </c>
+      <c r="B354" s="3">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="C354" s="3">
+        <v>0.36458333333333331</v>
+      </c>
+      <c r="D354" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="355" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A355" t="s">
+        <v>19</v>
+      </c>
+      <c r="B355" s="3">
+        <v>0.40625</v>
+      </c>
+      <c r="C355" s="3">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D355" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="356" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A356" t="s">
+        <v>137</v>
+      </c>
+      <c r="B356" s="3">
+        <v>0.5625</v>
+      </c>
+      <c r="C356" s="3">
+        <v>0.57291666666666663</v>
+      </c>
+      <c r="D356" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="357" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A357" t="s">
+        <v>19</v>
+      </c>
+      <c r="B357" s="3">
+        <v>0.625</v>
+      </c>
+      <c r="C357" s="3">
+        <v>0.65625</v>
+      </c>
+      <c r="D357" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="358" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A358" s="2">
+        <v>45764</v>
+      </c>
+    </row>
+    <row r="359" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A359" t="s">
+        <v>245</v>
+      </c>
+      <c r="B359" s="3">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="C359" s="3">
+        <v>0.375</v>
+      </c>
+      <c r="D359" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="360" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A360" t="s">
+        <v>34</v>
+      </c>
+      <c r="B360" s="3">
+        <v>0.375</v>
+      </c>
+      <c r="C360" s="3">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="D360" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="361" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A361" t="s">
+        <v>19</v>
+      </c>
+      <c r="B361" s="3">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="C361" s="3">
+        <v>0.4375</v>
+      </c>
+      <c r="D361" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="362" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A362" t="s">
+        <v>19</v>
+      </c>
+      <c r="B362" s="3">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="C362" s="3">
+        <v>0.55208333333333337</v>
+      </c>
+      <c r="D362" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="363" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A363" t="s">
+        <v>270</v>
+      </c>
+      <c r="B363" s="3">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="C363" s="3">
+        <v>0.5625</v>
+      </c>
+      <c r="D363" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="364" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A364" s="2">
+        <v>45769</v>
+      </c>
+    </row>
+    <row r="365" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A365" t="s">
+        <v>19</v>
+      </c>
+      <c r="B365" s="3">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="C365" s="3">
+        <v>0.34375</v>
+      </c>
+      <c r="D365" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="366" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A366" t="s">
+        <v>19</v>
+      </c>
+      <c r="B366" s="3">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="C366" s="3">
+        <v>0.34375</v>
+      </c>
+      <c r="D366" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="367" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A367" t="s">
+        <v>21</v>
+      </c>
+      <c r="B367" s="3">
+        <v>0.34375</v>
+      </c>
+      <c r="C367" s="3">
+        <v>0.36458333333333331</v>
+      </c>
+      <c r="D367" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="368" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A368" t="s">
+        <v>19</v>
+      </c>
+      <c r="B368" s="3">
+        <v>0.36458333333333331</v>
+      </c>
+      <c r="C368" s="3">
+        <v>0.375</v>
+      </c>
+      <c r="D368" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="369" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A369" t="s">
+        <v>19</v>
+      </c>
+      <c r="B369" s="3">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="C369" s="3">
+        <v>0.40625</v>
+      </c>
+      <c r="D369" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="370" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A370" t="s">
+        <v>19</v>
+      </c>
+      <c r="B370" s="3">
+        <v>0.40625</v>
+      </c>
+      <c r="C370" s="3">
+        <v>0.4375</v>
+      </c>
+      <c r="D370" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="371" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A371" t="s">
+        <v>19</v>
+      </c>
+      <c r="B371" s="3">
+        <v>0.4375</v>
+      </c>
+      <c r="C371" s="3">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D371" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="372" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A372" t="s">
+        <v>19</v>
+      </c>
+      <c r="B372" s="3">
+        <v>0.46875</v>
+      </c>
+      <c r="C372" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="D372" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="373" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A373" t="s">
+        <v>19</v>
+      </c>
+      <c r="B373" s="3">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="C373" s="3">
+        <v>0.61458333333333337</v>
+      </c>
+      <c r="D373" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="374" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A374" t="s">
+        <v>19</v>
+      </c>
+      <c r="B374" s="3">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="C374" s="3">
+        <v>0.61458333333333337</v>
+      </c>
+      <c r="D374" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="375" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A375" t="s">
+        <v>245</v>
+      </c>
+      <c r="B375" s="3">
+        <v>0.65625</v>
+      </c>
+      <c r="C375" s="3">
+        <v>0.67708333333333337</v>
+      </c>
+      <c r="D375" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="376" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A376" s="2">
+        <v>45769</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
